--- a/reports/二级子公司D_现金流量表_2026-07.xlsx
+++ b/reports/二级子公司D_现金流量表_2026-07.xlsx
@@ -1957,16 +1957,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
-      <c r="G3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
+      <c r="F3" s="28" t="n"/>
+      <c r="G3" s="28" t="n"/>
       <c r="I3" s="5" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1996,10 +1988,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>80982720</v>
+        <v>79017115</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>472013568</v>
+        <v>458396718</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2030,10 +2022,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>1599820</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>9955970</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2063,10 +2055,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>806900</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>4982070</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2096,10 +2088,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>400736</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>2489325</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2129,10 +2121,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>321908</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>1992418</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2162,10 +2154,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>241184</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>1493978</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2195,10 +2187,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>160442</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>995930</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2228,10 +2220,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>120949</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>747194</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2261,10 +2253,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>80026</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>497847</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2294,10 +2286,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>201910</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>1245547</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2327,10 +2319,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>100477</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>625435</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2360,10 +2352,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>64174</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>396024</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2393,10 +2385,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>207648</v>
+        <v>200870</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>1286676</v>
+        <v>1248748</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2426,10 +2418,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>1384320</v>
+        <v>1347134</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>8577840</v>
+        <v>8330196</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2546,7 +2538,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>82574688</v>
+        <v>84663645</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2577,10 +2569,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>53065600</v>
+        <v>51753929</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>328817200</v>
+        <v>319356766</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2610,10 +2602,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>533144</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>3318685</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2643,10 +2635,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>403818</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>2491166</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2676,10 +2668,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>266757</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>1659372</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2709,10 +2701,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>201578</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>1245453</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2742,10 +2734,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>133704</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>829837</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2775,10 +2767,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>101007</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>625769</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2808,10 +2800,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>8305920</v>
+        <v>8074778</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>51467040</v>
+        <v>49970481</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2841,10 +2833,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>4383680</v>
+        <v>4244066</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>27163160</v>
+        <v>26367080</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2874,10 +2866,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>1730400</v>
+        <v>1686684</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>10722300</v>
+        <v>10413165</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2936,7 +2928,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>67485600</v>
+        <v>67399465</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2967,7 +2959,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>15089088</v>
+        <v>17264180</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -3093,10 +3085,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>82400</v>
+        <v>80021</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>576800</v>
+        <v>560059</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3159,10 +3151,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>721000</v>
+        <v>702259</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>5047000</v>
+        <v>4901705</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3192,10 +3184,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>432600</v>
+        <v>418204</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>3028200</v>
+        <v>2938768</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3225,7 +3217,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>803400</v>
+        <v>782280</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3256,10 +3248,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>8240000</v>
+        <v>7960221</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>57680000</v>
+        <v>55976089</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3289,10 +3281,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>1236000</v>
+        <v>1205454</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>8652000</v>
+        <v>8403049</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3322,10 +3314,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>5665000</v>
+        <v>5479966</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>39655000</v>
+        <v>38489953</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3454,10 +3446,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>185400</v>
+        <v>180418</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>1297800</v>
+        <v>1260351</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3487,7 +3479,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>8425400</v>
+        <v>8140639</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3518,7 +3510,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-7622000</v>
+        <v>-7358359</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3578,10 +3570,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>1545000</v>
+        <v>1507333</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>10815000</v>
+        <v>10504313</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3644,10 +3636,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>2575000</v>
+        <v>2508147</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>18025000</v>
+        <v>17503869</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3677,10 +3669,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>2575000</v>
+        <v>2495304</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>18025000</v>
+        <v>17498500</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3710,10 +3702,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>82400</v>
+        <v>80024</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>576800</v>
+        <v>559968</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3743,7 +3735,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>4202400</v>
+        <v>4095504</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3774,10 +3766,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>2060000</v>
+        <v>1994443</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>14420000</v>
+        <v>13995597</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3807,10 +3799,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>2060000</v>
+        <v>2007919</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>14420000</v>
+        <v>14005588</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3840,10 +3832,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>329600</v>
+        <v>318487</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>2307200</v>
+        <v>2239008</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3902,10 +3894,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>288400</v>
+        <v>278670</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>2018800</v>
+        <v>1959236</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3935,10 +3927,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>41200</v>
+        <v>40160</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>288400</v>
+        <v>280084</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3968,7 +3960,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>2430800</v>
+        <v>2353090</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3999,7 +3991,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>1771600</v>
+        <v>1742414</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -4059,7 +4051,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>9238688</v>
+        <v>11648235</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -4090,7 +4082,9 @@
         </is>
       </c>
       <c r="F69" s="23" t="n"/>
-      <c r="G69" s="20" t="n"/>
+      <c r="G69" s="20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
@@ -4119,7 +4113,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>9238688</v>
+        <v>11648235</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
